--- a/artfynd/A 21853-2022 artfynd.xlsx
+++ b/artfynd/A 21853-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 21853-2022 artfynd.xlsx
+++ b/artfynd/A 21853-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY43"/>
+  <dimension ref="A1:AY48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1656,60 +1656,48 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>101576989</v>
+        <v>131729213</v>
       </c>
       <c r="B10" t="n">
-        <v>89412</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>8453</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5442</v>
+        <v>106545</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Norr om Sanda, Nacka, Srm</t>
+          <t>Erstavik, Srm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>682931.966279577</v>
+        <v>682658</v>
       </c>
       <c r="R10" t="n">
-        <v>6575458.414300293</v>
+        <v>6575490</v>
       </c>
       <c r="S10" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1733,22 +1721,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2022-06-11</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>12:43</t>
+          <t>2025-10-16</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2022-06-11</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>12:43</t>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Äldre gnagspår</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1757,29 +1740,28 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kristina Bäck</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kristina Bäck, Ronny Fors, Johan Stork, Martin Permats, Jana Eriksson</t>
+          <t>Samuel Persson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>101575072</v>
+        <v>101576989</v>
       </c>
       <c r="B11" t="n">
-        <v>93375</v>
+        <v>89412</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1788,31 +1770,34 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2180</v>
+        <v>5442</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1820,10 +1805,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>682764.9159736893</v>
+        <v>682931.966279577</v>
       </c>
       <c r="R11" t="n">
-        <v>6575488.23749305</v>
+        <v>6575458.414300293</v>
       </c>
       <c r="S11" t="n">
         <v>2</v>
@@ -1855,7 +1840,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1865,7 +1850,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1893,10 +1878,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>101589135</v>
+        <v>101575072</v>
       </c>
       <c r="B12" t="n">
-        <v>96251</v>
+        <v>93375</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1909,52 +1894,41 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>219790</v>
+        <v>2180</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Nacka, Srm</t>
+          <t>Norr om Sanda, Nacka, Srm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>683165.6316249722</v>
+        <v>682764.9159736893</v>
       </c>
       <c r="R12" t="n">
-        <v>6575493.234575982</v>
+        <v>6575488.23749305</v>
       </c>
       <c r="S12" t="n">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1983,7 +1957,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1993,7 +1967,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2002,33 +1976,29 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AH12" t="inlineStr">
-        <is>
-          <t>Våtmark</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Martin Permats</t>
+          <t>Kristina Bäck</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Martin Permats</t>
+          <t>Kristina Bäck, Ronny Fors, Johan Stork, Martin Permats, Jana Eriksson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>101574857</v>
+        <v>101589135</v>
       </c>
       <c r="B13" t="n">
-        <v>93375</v>
+        <v>96251</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2041,41 +2011,52 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2180</v>
+        <v>219790</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Norr om Sanda, Srm</t>
+          <t>Nacka, Srm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>682708.4838155493</v>
+        <v>683165.6316249722</v>
       </c>
       <c r="R13" t="n">
-        <v>6575520.834938429</v>
+        <v>6575493.234575982</v>
       </c>
       <c r="S13" t="n">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2104,7 +2085,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2114,7 +2095,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2123,29 +2104,33 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>Våtmark</t>
+        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Kristina Bäck</t>
+          <t>Martin Permats</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Kristina Bäck, Johan Stork, Ronny Fors, Jana Eriksson, Martin Permats</t>
+          <t>Martin Permats</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>101578301</v>
+        <v>101574857</v>
       </c>
       <c r="B14" t="n">
-        <v>5113</v>
+        <v>93375</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2158,39 +2143,38 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100526</v>
+        <v>2180</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Norr om Sanda, Nacka, Srm</t>
+          <t>Norr om Sanda, Srm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>683191.6723238613</v>
+        <v>682708.4838155493</v>
       </c>
       <c r="R14" t="n">
-        <v>6575410.550240339</v>
+        <v>6575520.834938429</v>
       </c>
       <c r="S14" t="n">
         <v>2</v>
@@ -2222,7 +2206,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2232,7 +2216,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2253,17 +2237,17 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Kristina Bäck, Ronny Fors, Martin Permats, Jana Eriksson</t>
+          <t>Kristina Bäck, Johan Stork, Ronny Fors, Jana Eriksson, Martin Permats</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>101577019</v>
+        <v>101578301</v>
       </c>
       <c r="B15" t="n">
-        <v>89412</v>
+        <v>5113</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2272,38 +2256,32 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5442</v>
+        <v>100526</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2311,10 +2289,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>682934.5866666588</v>
+        <v>683191.6723238613</v>
       </c>
       <c r="R15" t="n">
-        <v>6575478.502218832</v>
+        <v>6575410.550240339</v>
       </c>
       <c r="S15" t="n">
         <v>2</v>
@@ -2346,7 +2324,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2356,7 +2334,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2377,17 +2355,17 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Kristina Bäck, Ronny Fors, Johan Stork, Jana Eriksson, Martin Permats</t>
+          <t>Kristina Bäck, Ronny Fors, Martin Permats, Jana Eriksson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>101589275</v>
+        <v>101577019</v>
       </c>
       <c r="B16" t="n">
-        <v>95519</v>
+        <v>89412</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2396,43 +2374,52 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221945</v>
+        <v>5442</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Nacka, Srm</t>
+          <t>Norr om Sanda, Nacka, Srm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>683165.6316249722</v>
+        <v>682934.5866666588</v>
       </c>
       <c r="R16" t="n">
-        <v>6575493.234575982</v>
+        <v>6575478.502218832</v>
       </c>
       <c r="S16" t="n">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2461,7 +2448,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2471,7 +2458,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2480,33 +2467,29 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
-      </c>
-      <c r="AH16" t="inlineStr">
-        <is>
-          <t>Våtmark</t>
-        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Martin Permats</t>
+          <t>Kristina Bäck</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Martin Permats</t>
+          <t>Kristina Bäck, Ronny Fors, Johan Stork, Jana Eriksson, Martin Permats</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>101577442</v>
+        <v>101589275</v>
       </c>
       <c r="B17" t="n">
-        <v>89412</v>
+        <v>95519</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2515,52 +2498,43 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5442</v>
+        <v>221945</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Norr om Sanda, Nacka, Srm</t>
+          <t>Nacka, Srm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>683020.7230944174</v>
+        <v>683165.6316249722</v>
       </c>
       <c r="R17" t="n">
-        <v>6575478.562571427</v>
+        <v>6575493.234575982</v>
       </c>
       <c r="S17" t="n">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2589,7 +2563,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2599,7 +2573,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2608,29 +2582,33 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>Våtmark</t>
+        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Kristina Bäck</t>
+          <t>Martin Permats</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Kristina Bäck, Ronny Fors, Johan Stork, Martin Permats, Jana Eriksson</t>
+          <t>Martin Permats</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>101577625</v>
+        <v>101577442</v>
       </c>
       <c r="B18" t="n">
-        <v>96251</v>
+        <v>89412</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2639,47 +2617,52 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>219790</v>
+        <v>5442</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Norr om Sanda, Nacka, Srm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>683044.7715829043</v>
+        <v>683020.7230944174</v>
       </c>
       <c r="R18" t="n">
-        <v>6575468.974419592</v>
+        <v>6575478.562571427</v>
       </c>
       <c r="S18" t="n">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2708,7 +2691,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2718,7 +2701,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2727,6 +2710,7 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2738,17 +2722,17 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Kristina Bäck</t>
+          <t>Kristina Bäck, Ronny Fors, Johan Stork, Martin Permats, Jana Eriksson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>101575316</v>
+        <v>101577625</v>
       </c>
       <c r="B19" t="n">
-        <v>56411</v>
+        <v>96251</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2757,45 +2741,47 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>219790</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Norr om Sanda, Nacka, Srm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>682761.9994682702</v>
+        <v>683044.7715829043</v>
       </c>
       <c r="R19" t="n">
-        <v>6575474.277554707</v>
+        <v>6575468.974419592</v>
       </c>
       <c r="S19" t="n">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2824,7 +2810,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2834,12 +2820,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:09</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Hackspår</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2859,17 +2840,17 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Kristina Bäck, Ronny Fors, Jana Eriksson, Martin Permats, Johan Stork</t>
+          <t>Kristina Bäck</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>101575253</v>
+        <v>101575316</v>
       </c>
       <c r="B20" t="n">
-        <v>8377</v>
+        <v>56411</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2878,29 +2859,28 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr"/>
@@ -2911,10 +2891,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>682777.8871047667</v>
+        <v>682761.9994682702</v>
       </c>
       <c r="R20" t="n">
-        <v>6575463.782761714</v>
+        <v>6575474.277554707</v>
       </c>
       <c r="S20" t="n">
         <v>2</v>
@@ -2946,7 +2926,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2956,7 +2936,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>12:09</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Hackspår</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2965,7 +2950,6 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2977,17 +2961,17 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Kristina Bäck, Ronny Fors, Johan Stork, Jana Eriksson, Martin Permats</t>
+          <t>Kristina Bäck, Ronny Fors, Jana Eriksson, Martin Permats, Johan Stork</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>101577080</v>
+        <v>101575253</v>
       </c>
       <c r="B21" t="n">
-        <v>4717</v>
+        <v>8377</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3000,21 +2984,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>102306</v>
+        <v>106545</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -3029,10 +3013,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>682934.5866666588</v>
+        <v>682777.8871047667</v>
       </c>
       <c r="R21" t="n">
-        <v>6575478.502218832</v>
+        <v>6575463.782761714</v>
       </c>
       <c r="S21" t="n">
         <v>2</v>
@@ -3064,7 +3048,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3074,12 +3058,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>12:43</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Hål efter i gran som är döende</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3107,10 +3086,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>101575295</v>
+        <v>101577080</v>
       </c>
       <c r="B22" t="n">
-        <v>89412</v>
+        <v>4717</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3119,38 +3098,32 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5442</v>
+        <v>102306</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Duftschmid, 1825)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -3158,10 +3131,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>682759.775949874</v>
+        <v>682934.5866666588</v>
       </c>
       <c r="R22" t="n">
-        <v>6575488.501670112</v>
+        <v>6575478.502218832</v>
       </c>
       <c r="S22" t="n">
         <v>2</v>
@@ -3193,7 +3166,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3203,7 +3176,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>12:43</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Hål efter i gran som är döende</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3224,17 +3202,17 @@
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Kristina Bäck, Jana Eriksson, Ronny Fors, Martin Permats, Johan Stork</t>
+          <t>Kristina Bäck, Ronny Fors, Johan Stork, Jana Eriksson, Martin Permats</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>101577753</v>
+        <v>101575295</v>
       </c>
       <c r="B23" t="n">
-        <v>95519</v>
+        <v>89412</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3243,31 +3221,38 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>221945</v>
+        <v>5442</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -3275,10 +3260,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>683078.6567980717</v>
+        <v>682759.775949874</v>
       </c>
       <c r="R23" t="n">
-        <v>6575468.050526729</v>
+        <v>6575488.501670112</v>
       </c>
       <c r="S23" t="n">
         <v>2</v>
@@ -3310,7 +3295,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3320,7 +3305,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3341,17 +3326,17 @@
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Kristina Bäck, Ronny Fors, Johan Stork, Martin Permats, Jana Eriksson</t>
+          <t>Kristina Bäck, Jana Eriksson, Ronny Fors, Martin Permats, Johan Stork</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>101577998</v>
+        <v>101577753</v>
       </c>
       <c r="B24" t="n">
-        <v>4717</v>
+        <v>95519</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3364,32 +3349,27 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>102306</v>
+        <v>221945</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3397,10 +3377,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>683132.831303214</v>
+        <v>683078.6567980717</v>
       </c>
       <c r="R24" t="n">
-        <v>6575471.68927494</v>
+        <v>6575468.050526729</v>
       </c>
       <c r="S24" t="n">
         <v>2</v>
@@ -3432,7 +3412,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3442,7 +3422,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3463,17 +3443,17 @@
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Kristina Bäck, Ronny Fors, Johan Stork, Jana Eriksson, Martin Permats</t>
+          <t>Kristina Bäck, Ronny Fors, Johan Stork, Martin Permats, Jana Eriksson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>101575063</v>
+        <v>101577998</v>
       </c>
       <c r="B25" t="n">
-        <v>8367</v>
+        <v>4717</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3486,24 +3466,25 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>106554</v>
+        <v>102306</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
@@ -3511,19 +3492,20 @@
           <t>äldre gnagspår</t>
         </is>
       </c>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Sanda, norr om, Srm</t>
+          <t>Norr om Sanda, Nacka, Srm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>682734.8529345258</v>
+        <v>683132.831303214</v>
       </c>
       <c r="R25" t="n">
-        <v>6575494.97837727</v>
+        <v>6575471.68927494</v>
       </c>
       <c r="S25" t="n">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3552,7 +3534,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3562,7 +3544,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3571,28 +3553,29 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Johan Stork</t>
+          <t>Kristina Bäck</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Johan Stork</t>
+          <t>Kristina Bäck, Ronny Fors, Johan Stork, Jana Eriksson, Martin Permats</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>101577329</v>
+        <v>101575063</v>
       </c>
       <c r="B26" t="n">
-        <v>93375</v>
+        <v>8367</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3605,36 +3588,41 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2180</v>
+        <v>106554</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Sanda, norr om, Srm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>682951.9222491342</v>
+        <v>682734.8529345258</v>
       </c>
       <c r="R26" t="n">
-        <v>6575448.628163522</v>
+        <v>6575494.97837727</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3703,7 +3691,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>101576764</v>
+        <v>101577329</v>
       </c>
       <c r="B27" t="n">
         <v>93375</v>
@@ -3745,10 +3733,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>682892.7275595821</v>
+        <v>682951.9222491342</v>
       </c>
       <c r="R27" t="n">
-        <v>6575495.933338026</v>
+        <v>6575448.628163522</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3817,10 +3805,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>101576478</v>
+        <v>101576764</v>
       </c>
       <c r="B28" t="n">
-        <v>89412</v>
+        <v>93375</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3829,48 +3817,40 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5442</v>
+        <v>2180</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Sanda, norr om, Srm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>682931.6159086931</v>
+        <v>682892.7275595821</v>
       </c>
       <c r="R28" t="n">
-        <v>6575476.311617732</v>
+        <v>6575495.933338026</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3939,57 +3919,48 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>101574878</v>
+        <v>131729211</v>
       </c>
       <c r="B29" t="n">
-        <v>93375</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
-        </is>
+        <v>91849</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2180</v>
+        <v>5442</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Norr om Sanda, Nacka, Srm</t>
+          <t>Erstavik, Srm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>682710.461164355</v>
+        <v>682932</v>
       </c>
       <c r="R29" t="n">
-        <v>6575511.717336961</v>
+        <v>6575476</v>
       </c>
       <c r="S29" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4013,22 +3984,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2022-06-11</t>
-        </is>
-      </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>11:37</t>
+          <t>2025-10-16</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2022-06-11</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>11:37</t>
+          <t>2025-10-16</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4037,33 +3998,32 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Kristina Bäck</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Kristina Bäck, Jana Eriksson, Johan Stork, Ronny Fors, Martin Permats</t>
+          <t>Samuel Persson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>111858253</v>
+        <v>101574878</v>
       </c>
       <c r="B30" t="n">
-        <v>89936</v>
+        <v>93375</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4072,48 +4032,41 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5420</v>
+        <v>2180</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>NW Erstavik, Srm</t>
+          <t>Norr om Sanda, Nacka, Srm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>682892</v>
+        <v>682710.461164355</v>
       </c>
       <c r="R30" t="n">
-        <v>6575488</v>
+        <v>6575511.717336961</v>
       </c>
       <c r="S30" t="n">
-        <v>50</v>
+        <v>2</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4137,17 +4090,22 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2023-09-02</t>
+          <t>2022-06-11</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2023-09-02</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Hällmark, stig; På Tallstubbe, "tung-formad"</t>
+          <t>2022-06-11</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4163,22 +4121,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Henry Gudmundson</t>
+          <t>Kristina Bäck</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Henry Gudmundson</t>
+          <t>Kristina Bäck, Jana Eriksson, Johan Stork, Ronny Fors, Martin Permats</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>112017130</v>
+        <v>111858253</v>
       </c>
       <c r="B31" t="n">
-        <v>90815</v>
+        <v>89936</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4191,40 +4149,48 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4364</v>
+        <v>5420</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
+          <t>(Fr.) Pat.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>N Mellanberg, Erstavik, Srm</t>
+          <t>NW Erstavik, Srm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>682695</v>
+        <v>682892</v>
       </c>
       <c r="R31" t="n">
-        <v>6575454</v>
+        <v>6575488</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4248,12 +4214,17 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2023-09-10</t>
+          <t>2023-09-02</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2023-09-10</t>
+          <t>2023-09-02</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Hällmark, stig; På Tallstubbe, "tung-formad"</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4269,22 +4240,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Ronny Fors</t>
+          <t>Henry Gudmundson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Ronny Fors</t>
+          <t>Henry Gudmundson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>112017512</v>
+        <v>112017130</v>
       </c>
       <c r="B32" t="n">
-        <v>88181</v>
+        <v>90815</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4293,37 +4264,29 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6276</v>
+        <v>4364</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
@@ -4332,10 +4295,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>683037</v>
+        <v>682695</v>
       </c>
       <c r="R32" t="n">
-        <v>6575484</v>
+        <v>6575454</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4395,10 +4358,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>112017447</v>
+        <v>112017512</v>
       </c>
       <c r="B33" t="n">
-        <v>90815</v>
+        <v>88181</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4407,29 +4370,37 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>4364</v>
+        <v>6276</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
@@ -4438,10 +4409,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>682844</v>
+        <v>683037</v>
       </c>
       <c r="R33" t="n">
-        <v>6575514</v>
+        <v>6575484</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4501,10 +4472,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>112017326</v>
+        <v>112017447</v>
       </c>
       <c r="B34" t="n">
-        <v>90809</v>
+        <v>90815</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4513,25 +4484,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4544,10 +4515,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>682714</v>
+        <v>682844</v>
       </c>
       <c r="R34" t="n">
-        <v>6575496</v>
+        <v>6575514</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4607,10 +4578,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>112017465</v>
+        <v>112017326</v>
       </c>
       <c r="B35" t="n">
-        <v>88181</v>
+        <v>90809</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4619,37 +4590,29 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6276</v>
+        <v>4362</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Hornem.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
@@ -4658,10 +4621,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>682896</v>
+        <v>682714</v>
       </c>
       <c r="R35" t="n">
-        <v>6575514</v>
+        <v>6575496</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4721,10 +4684,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>112017252</v>
+        <v>112017465</v>
       </c>
       <c r="B36" t="n">
-        <v>90815</v>
+        <v>88181</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4733,29 +4696,37 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>4364</v>
+        <v>6276</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K36" t="inlineStr"/>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
@@ -4764,10 +4735,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>682711</v>
+        <v>682896</v>
       </c>
       <c r="R36" t="n">
-        <v>6575494</v>
+        <v>6575514</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4827,10 +4798,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>112017224</v>
+        <v>112017252</v>
       </c>
       <c r="B37" t="n">
-        <v>90827</v>
+        <v>90815</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4843,21 +4814,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4870,10 +4841,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>682703</v>
+        <v>682711</v>
       </c>
       <c r="R37" t="n">
-        <v>6575491</v>
+        <v>6575494</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4933,10 +4904,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>112017534</v>
+        <v>112017224</v>
       </c>
       <c r="B38" t="n">
-        <v>88141</v>
+        <v>90827</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4945,37 +4916,29 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1593</v>
+        <v>4366</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Lakritsmusseron</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Tricholoma apium</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Jul.Schäff.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
@@ -4984,10 +4947,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>683073</v>
+        <v>682703</v>
       </c>
       <c r="R38" t="n">
-        <v>6575478</v>
+        <v>6575491</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5047,10 +5010,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>112017413</v>
+        <v>112017534</v>
       </c>
       <c r="B39" t="n">
-        <v>90858</v>
+        <v>88141</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5059,29 +5022,37 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5448</v>
+        <v>1593</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Lakritsmusseron</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Tricholoma apium</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
+          <t>Jul.Schäff.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K39" t="inlineStr"/>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
@@ -5090,10 +5061,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>682734</v>
+        <v>683073</v>
       </c>
       <c r="R39" t="n">
-        <v>6575482</v>
+        <v>6575478</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5153,10 +5124,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>112017488</v>
+        <v>112017413</v>
       </c>
       <c r="B40" t="n">
-        <v>90827</v>
+        <v>90858</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5165,25 +5136,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>4366</v>
+        <v>5448</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Phellodon connatus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Schultz) nom.prov</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5196,10 +5167,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>682956</v>
+        <v>682734</v>
       </c>
       <c r="R40" t="n">
-        <v>6575474</v>
+        <v>6575482</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5259,10 +5230,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>112017159</v>
+        <v>112017488</v>
       </c>
       <c r="B41" t="n">
-        <v>90859</v>
+        <v>90827</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5271,25 +5242,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5449</v>
+        <v>4366</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5302,10 +5273,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>682699</v>
+        <v>682956</v>
       </c>
       <c r="R41" t="n">
-        <v>6575482</v>
+        <v>6575474</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5365,7 +5336,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>112017392</v>
+        <v>112017159</v>
       </c>
       <c r="B42" t="n">
         <v>90859</v>
@@ -5408,10 +5379,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>682712</v>
+        <v>682699</v>
       </c>
       <c r="R42" t="n">
-        <v>6575458</v>
+        <v>6575482</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5471,10 +5442,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>112017430</v>
+        <v>112017392</v>
       </c>
       <c r="B43" t="n">
-        <v>90858</v>
+        <v>90859</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5487,21 +5458,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>5448</v>
+        <v>5449</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5514,10 +5485,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>682793</v>
+        <v>682712</v>
       </c>
       <c r="R43" t="n">
-        <v>6575520</v>
+        <v>6575458</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5574,6 +5545,500 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>112017430</v>
+      </c>
+      <c r="B44" t="n">
+        <v>90858</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>5448</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Svartvit taggsvamp</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Phellodon connatus</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Schultz) nom.prov</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>N Mellanberg, Erstavik, Srm</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>682793</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6575520</v>
+      </c>
+      <c r="S44" t="n">
+        <v>10</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Nacka</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Nacka</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2023-09-10</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2023-09-10</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF44" t="inlineStr"/>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Ronny Fors</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Ronny Fors</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>131729207</v>
+      </c>
+      <c r="B45" t="n">
+        <v>91849</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Erstavik, Srm</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>683082</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6575501</v>
+      </c>
+      <c r="S45" t="n">
+        <v>5</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Nacka</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Nacka</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Johan Kjetselberg</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>131729210</v>
+      </c>
+      <c r="B46" t="n">
+        <v>91849</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Erstavik, Srm</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>683025</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6575474</v>
+      </c>
+      <c r="S46" t="n">
+        <v>5</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Nacka</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Nacka</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Johan Kjetselberg</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>131729208</v>
+      </c>
+      <c r="B47" t="n">
+        <v>93154</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Erstavik, Srm</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>683052</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6575490</v>
+      </c>
+      <c r="S47" t="n">
+        <v>5</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Nacka</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Nacka</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Johan Kjetselberg</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>131729209</v>
+      </c>
+      <c r="B48" t="n">
+        <v>93116</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Erstavik, Srm</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>683048</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6575489</v>
+      </c>
+      <c r="S48" t="n">
+        <v>5</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Nacka</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Nacka</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Johan Kjetselberg</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 21853-2022 artfynd.xlsx
+++ b/artfynd/A 21853-2022 artfynd.xlsx
@@ -1659,7 +1659,7 @@
         <v>131729213</v>
       </c>
       <c r="B10" t="n">
-        <v>8453</v>
+        <v>8454</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -3922,7 +3922,7 @@
         <v>131729211</v>
       </c>
       <c r="B29" t="n">
-        <v>91849</v>
+        <v>91850</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -5657,7 +5657,7 @@
         <v>131729207</v>
       </c>
       <c r="B45" t="n">
-        <v>91849</v>
+        <v>91850</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5751,10 +5751,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>131729210</v>
+        <v>131729208</v>
       </c>
       <c r="B46" t="n">
-        <v>91849</v>
+        <v>93155</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5762,21 +5762,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>5442</v>
+        <v>5966</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5786,10 +5786,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>683025</v>
+        <v>683052</v>
       </c>
       <c r="R46" t="n">
-        <v>6575474</v>
+        <v>6575490</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5848,10 +5848,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>131729208</v>
+        <v>131729210</v>
       </c>
       <c r="B47" t="n">
-        <v>93154</v>
+        <v>91850</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5859,21 +5859,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>5966</v>
+        <v>5442</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5883,10 +5883,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>683052</v>
+        <v>683025</v>
       </c>
       <c r="R47" t="n">
-        <v>6575490</v>
+        <v>6575474</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5948,7 +5948,7 @@
         <v>131729209</v>
       </c>
       <c r="B48" t="n">
-        <v>93116</v>
+        <v>93117</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>

--- a/artfynd/A 21853-2022 artfynd.xlsx
+++ b/artfynd/A 21853-2022 artfynd.xlsx
@@ -3922,7 +3922,7 @@
         <v>131729211</v>
       </c>
       <c r="B29" t="n">
-        <v>91850</v>
+        <v>91853</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -5657,7 +5657,7 @@
         <v>131729207</v>
       </c>
       <c r="B45" t="n">
-        <v>91850</v>
+        <v>91853</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5751,10 +5751,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>131729208</v>
+        <v>131729210</v>
       </c>
       <c r="B46" t="n">
-        <v>93155</v>
+        <v>91853</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5762,21 +5762,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>5966</v>
+        <v>5442</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5786,10 +5786,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>683052</v>
+        <v>683025</v>
       </c>
       <c r="R46" t="n">
-        <v>6575490</v>
+        <v>6575474</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5848,10 +5848,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>131729210</v>
+        <v>131729208</v>
       </c>
       <c r="B47" t="n">
-        <v>91850</v>
+        <v>93158</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5859,21 +5859,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>5442</v>
+        <v>5966</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5883,10 +5883,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>683025</v>
+        <v>683052</v>
       </c>
       <c r="R47" t="n">
-        <v>6575474</v>
+        <v>6575490</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5948,7 +5948,7 @@
         <v>131729209</v>
       </c>
       <c r="B48" t="n">
-        <v>93117</v>
+        <v>93120</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>

--- a/artfynd/A 21853-2022 artfynd.xlsx
+++ b/artfynd/A 21853-2022 artfynd.xlsx
@@ -5751,10 +5751,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>131729210</v>
+        <v>131729208</v>
       </c>
       <c r="B46" t="n">
-        <v>91853</v>
+        <v>93158</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5762,21 +5762,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>5442</v>
+        <v>5966</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5786,10 +5786,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>683025</v>
+        <v>683052</v>
       </c>
       <c r="R46" t="n">
-        <v>6575474</v>
+        <v>6575490</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5848,10 +5848,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>131729208</v>
+        <v>131729210</v>
       </c>
       <c r="B47" t="n">
-        <v>93158</v>
+        <v>91853</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5859,21 +5859,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>5966</v>
+        <v>5442</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5883,10 +5883,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>683052</v>
+        <v>683025</v>
       </c>
       <c r="R47" t="n">
-        <v>6575490</v>
+        <v>6575474</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>

--- a/artfynd/A 21853-2022 artfynd.xlsx
+++ b/artfynd/A 21853-2022 artfynd.xlsx
@@ -3922,7 +3922,7 @@
         <v>131729211</v>
       </c>
       <c r="B29" t="n">
-        <v>91853</v>
+        <v>91859</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -5657,7 +5657,7 @@
         <v>131729207</v>
       </c>
       <c r="B45" t="n">
-        <v>91853</v>
+        <v>91859</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5751,10 +5751,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>131729208</v>
+        <v>131729210</v>
       </c>
       <c r="B46" t="n">
-        <v>93158</v>
+        <v>91859</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5762,21 +5762,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>5966</v>
+        <v>5442</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5786,10 +5786,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>683052</v>
+        <v>683025</v>
       </c>
       <c r="R46" t="n">
-        <v>6575490</v>
+        <v>6575474</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5848,10 +5848,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>131729210</v>
+        <v>131729208</v>
       </c>
       <c r="B47" t="n">
-        <v>91853</v>
+        <v>93164</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5859,21 +5859,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>5442</v>
+        <v>5966</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5883,10 +5883,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>683025</v>
+        <v>683052</v>
       </c>
       <c r="R47" t="n">
-        <v>6575474</v>
+        <v>6575490</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5948,7 +5948,7 @@
         <v>131729209</v>
       </c>
       <c r="B48" t="n">
-        <v>93120</v>
+        <v>93126</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>

--- a/artfynd/A 21853-2022 artfynd.xlsx
+++ b/artfynd/A 21853-2022 artfynd.xlsx
@@ -5751,10 +5751,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>131729210</v>
+        <v>131729208</v>
       </c>
       <c r="B46" t="n">
-        <v>91859</v>
+        <v>93164</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5762,21 +5762,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>5442</v>
+        <v>5966</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5786,10 +5786,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>683025</v>
+        <v>683052</v>
       </c>
       <c r="R46" t="n">
-        <v>6575474</v>
+        <v>6575490</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5848,10 +5848,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>131729208</v>
+        <v>131729210</v>
       </c>
       <c r="B47" t="n">
-        <v>93164</v>
+        <v>91859</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5859,21 +5859,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>5966</v>
+        <v>5442</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5883,10 +5883,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>683052</v>
+        <v>683025</v>
       </c>
       <c r="R47" t="n">
-        <v>6575490</v>
+        <v>6575474</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>

--- a/artfynd/A 21853-2022 artfynd.xlsx
+++ b/artfynd/A 21853-2022 artfynd.xlsx
@@ -5751,10 +5751,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>131729208</v>
+        <v>131729210</v>
       </c>
       <c r="B46" t="n">
-        <v>93164</v>
+        <v>91859</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5762,21 +5762,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>5966</v>
+        <v>5442</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5786,10 +5786,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>683052</v>
+        <v>683025</v>
       </c>
       <c r="R46" t="n">
-        <v>6575490</v>
+        <v>6575474</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5848,10 +5848,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>131729210</v>
+        <v>131729208</v>
       </c>
       <c r="B47" t="n">
-        <v>91859</v>
+        <v>93164</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5859,21 +5859,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>5442</v>
+        <v>5966</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5883,10 +5883,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>683025</v>
+        <v>683052</v>
       </c>
       <c r="R47" t="n">
-        <v>6575474</v>
+        <v>6575490</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>

--- a/artfynd/A 21853-2022 artfynd.xlsx
+++ b/artfynd/A 21853-2022 artfynd.xlsx
@@ -1659,7 +1659,7 @@
         <v>131729213</v>
       </c>
       <c r="B10" t="n">
-        <v>8454</v>
+        <v>8455</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -3922,7 +3922,7 @@
         <v>131729211</v>
       </c>
       <c r="B29" t="n">
-        <v>91859</v>
+        <v>91862</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -5657,7 +5657,7 @@
         <v>131729207</v>
       </c>
       <c r="B45" t="n">
-        <v>91859</v>
+        <v>91862</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5751,10 +5751,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>131729208</v>
+        <v>131729210</v>
       </c>
       <c r="B46" t="n">
-        <v>93164</v>
+        <v>91862</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5762,21 +5762,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>5966</v>
+        <v>5442</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5786,10 +5786,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>683052</v>
+        <v>683025</v>
       </c>
       <c r="R46" t="n">
-        <v>6575490</v>
+        <v>6575474</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5848,10 +5848,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>131729210</v>
+        <v>131729208</v>
       </c>
       <c r="B47" t="n">
-        <v>91859</v>
+        <v>93167</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5859,21 +5859,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>5442</v>
+        <v>5966</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5883,10 +5883,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>683025</v>
+        <v>683052</v>
       </c>
       <c r="R47" t="n">
-        <v>6575474</v>
+        <v>6575490</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5948,7 +5948,7 @@
         <v>131729209</v>
       </c>
       <c r="B48" t="n">
-        <v>93126</v>
+        <v>93129</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>

--- a/artfynd/A 21853-2022 artfynd.xlsx
+++ b/artfynd/A 21853-2022 artfynd.xlsx
@@ -3922,7 +3922,7 @@
         <v>131729211</v>
       </c>
       <c r="B29" t="n">
-        <v>91862</v>
+        <v>91867</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -5657,7 +5657,7 @@
         <v>131729207</v>
       </c>
       <c r="B45" t="n">
-        <v>91862</v>
+        <v>91867</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5751,10 +5751,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>131729210</v>
+        <v>131729208</v>
       </c>
       <c r="B46" t="n">
-        <v>91862</v>
+        <v>93172</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5762,21 +5762,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>5442</v>
+        <v>5966</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5786,10 +5786,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>683025</v>
+        <v>683052</v>
       </c>
       <c r="R46" t="n">
-        <v>6575474</v>
+        <v>6575490</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5848,10 +5848,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>131729208</v>
+        <v>131729210</v>
       </c>
       <c r="B47" t="n">
-        <v>93167</v>
+        <v>91867</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5859,21 +5859,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>5966</v>
+        <v>5442</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5883,10 +5883,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>683052</v>
+        <v>683025</v>
       </c>
       <c r="R47" t="n">
-        <v>6575490</v>
+        <v>6575474</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5948,7 +5948,7 @@
         <v>131729209</v>
       </c>
       <c r="B48" t="n">
-        <v>93129</v>
+        <v>93134</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>

--- a/artfynd/A 21853-2022 artfynd.xlsx
+++ b/artfynd/A 21853-2022 artfynd.xlsx
@@ -3922,7 +3922,7 @@
         <v>131729211</v>
       </c>
       <c r="B29" t="n">
-        <v>91867</v>
+        <v>91869</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -5657,7 +5657,7 @@
         <v>131729207</v>
       </c>
       <c r="B45" t="n">
-        <v>91867</v>
+        <v>91869</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5751,10 +5751,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>131729208</v>
+        <v>131729210</v>
       </c>
       <c r="B46" t="n">
-        <v>93172</v>
+        <v>91869</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5762,21 +5762,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>5966</v>
+        <v>5442</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5786,10 +5786,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>683052</v>
+        <v>683025</v>
       </c>
       <c r="R46" t="n">
-        <v>6575490</v>
+        <v>6575474</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5848,10 +5848,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>131729210</v>
+        <v>131729208</v>
       </c>
       <c r="B47" t="n">
-        <v>91867</v>
+        <v>93174</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5859,21 +5859,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>5442</v>
+        <v>5966</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5883,10 +5883,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>683025</v>
+        <v>683052</v>
       </c>
       <c r="R47" t="n">
-        <v>6575474</v>
+        <v>6575490</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5948,7 +5948,7 @@
         <v>131729209</v>
       </c>
       <c r="B48" t="n">
-        <v>93134</v>
+        <v>93136</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>

--- a/artfynd/A 21853-2022 artfynd.xlsx
+++ b/artfynd/A 21853-2022 artfynd.xlsx
@@ -3922,7 +3922,7 @@
         <v>131729211</v>
       </c>
       <c r="B29" t="n">
-        <v>91869</v>
+        <v>91905</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -5657,7 +5657,7 @@
         <v>131729207</v>
       </c>
       <c r="B45" t="n">
-        <v>91869</v>
+        <v>91905</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5751,10 +5751,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>131729210</v>
+        <v>131729208</v>
       </c>
       <c r="B46" t="n">
-        <v>91869</v>
+        <v>93210</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5762,21 +5762,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>5442</v>
+        <v>5966</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5786,10 +5786,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>683025</v>
+        <v>683052</v>
       </c>
       <c r="R46" t="n">
-        <v>6575474</v>
+        <v>6575490</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5848,10 +5848,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>131729208</v>
+        <v>131729210</v>
       </c>
       <c r="B47" t="n">
-        <v>93174</v>
+        <v>91905</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5859,21 +5859,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>5966</v>
+        <v>5442</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5883,10 +5883,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>683052</v>
+        <v>683025</v>
       </c>
       <c r="R47" t="n">
-        <v>6575490</v>
+        <v>6575474</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5948,7 +5948,7 @@
         <v>131729209</v>
       </c>
       <c r="B48" t="n">
-        <v>93136</v>
+        <v>93172</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>

--- a/artfynd/A 21853-2022 artfynd.xlsx
+++ b/artfynd/A 21853-2022 artfynd.xlsx
@@ -3922,7 +3922,7 @@
         <v>131729211</v>
       </c>
       <c r="B29" t="n">
-        <v>91905</v>
+        <v>91910</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -5657,7 +5657,7 @@
         <v>131729207</v>
       </c>
       <c r="B45" t="n">
-        <v>91905</v>
+        <v>91910</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5754,7 +5754,7 @@
         <v>131729208</v>
       </c>
       <c r="B46" t="n">
-        <v>93210</v>
+        <v>93215</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5851,7 +5851,7 @@
         <v>131729210</v>
       </c>
       <c r="B47" t="n">
-        <v>91905</v>
+        <v>91910</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5948,7 +5948,7 @@
         <v>131729209</v>
       </c>
       <c r="B48" t="n">
-        <v>93172</v>
+        <v>93177</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>

--- a/artfynd/A 21853-2022 artfynd.xlsx
+++ b/artfynd/A 21853-2022 artfynd.xlsx
@@ -3922,7 +3922,7 @@
         <v>131729211</v>
       </c>
       <c r="B29" t="n">
-        <v>91910</v>
+        <v>91913</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -5657,7 +5657,7 @@
         <v>131729207</v>
       </c>
       <c r="B45" t="n">
-        <v>91910</v>
+        <v>91913</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5754,7 +5754,7 @@
         <v>131729210</v>
       </c>
       <c r="B46" t="n">
-        <v>91910</v>
+        <v>91913</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5851,7 +5851,7 @@
         <v>131729208</v>
       </c>
       <c r="B47" t="n">
-        <v>93215</v>
+        <v>93218</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5948,7 +5948,7 @@
         <v>131729209</v>
       </c>
       <c r="B48" t="n">
-        <v>93177</v>
+        <v>93180</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>

--- a/artfynd/A 21853-2022 artfynd.xlsx
+++ b/artfynd/A 21853-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY48"/>
+  <dimension ref="A1:AY56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>101574354</v>
+        <v>128469507</v>
       </c>
       <c r="B2" t="n">
-        <v>89412</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92699</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5442</v>
+        <v>366</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Kandelabersvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Artomyces pyxidatus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Pers.) Jülich</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -718,21 +713,19 @@
           <t>fruktkroppar</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Norr om Sanda, Nacka, Srm</t>
+          <t>Kattrumpan, Kattrumpan, Srm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>682670.3787457519</v>
+        <v>683117</v>
       </c>
       <c r="R2" t="n">
-        <v>6575428.405818475</v>
+        <v>6575586</v>
       </c>
       <c r="S2" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -756,22 +749,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2022-06-11</t>
+          <t>2025-09-14</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2022-06-11</t>
+          <t>2025-09-14</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -780,61 +773,60 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kristina Bäck</t>
+          <t>Johan Lilyvalley</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kristina Bäck, Ronny Fors, Martin Permats, Johan Stork, Jana Eriksson</t>
+          <t>Johan Lilyvalley</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>101574465</v>
+        <v>112017534</v>
       </c>
       <c r="B3" t="n">
-        <v>89412</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90659</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5442</v>
+        <v>1593</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Lakritsmusseron</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Tricholoma apium</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>Jul.Schäff.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -846,17 +838,17 @@
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Norr om Sanda, Nacka, Srm</t>
+          <t>N Mellanberg, Erstavik, Srm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>682666.0996635273</v>
+        <v>683073</v>
       </c>
       <c r="R3" t="n">
-        <v>6575464.028101741</v>
+        <v>6575478</v>
       </c>
       <c r="S3" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -880,22 +872,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2022-06-11</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>11:28</t>
+          <t>2023-09-10</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2022-06-11</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>11:28</t>
+          <t>2023-09-10</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -911,69 +893,69 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kristina Bäck</t>
+          <t>Ronny Fors</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kristina Bäck, Ronny Fors, Johan Stork, Martin Permats, Jana Eriksson</t>
+          <t>Ronny Fors</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>101574331</v>
+        <v>445675</v>
       </c>
       <c r="B4" t="n">
-        <v>56411</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90674</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>1596</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Jättemusseron</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tricholoma colossus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
+          <t>(Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Norr om Sanda, Nacka, Srm</t>
+          <t>Sandasjön O, Srm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>682664.638427674</v>
+        <v>682623</v>
       </c>
       <c r="R4" t="n">
-        <v>6575409.19141892</v>
+        <v>6575517</v>
       </c>
       <c r="S4" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -997,27 +979,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2022-06-11</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>11:19</t>
+          <t>2012-09-30</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2022-06-11</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>11:19</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Spår</t>
+          <t>2012-09-30</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1028,70 +995,70 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Hällmark</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kristina Bäck</t>
+          <t>Hans-Göran Toresson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kristina Bäck, Ronny Fors, Johan Stork, Martin Permats, Jana Eriksson</t>
+          <t>Hans-Göran Toresson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>101574766</v>
+        <v>101574857</v>
       </c>
       <c r="B5" t="n">
-        <v>56411</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>2180</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Norr om Sanda, Nacka, Srm</t>
+          <t>Norr om Sanda, Srm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>682681.4215081711</v>
+        <v>682708</v>
       </c>
       <c r="R5" t="n">
-        <v>6575518.507863252</v>
+        <v>6575521</v>
       </c>
       <c r="S5" t="n">
         <v>2</v>
@@ -1136,17 +1103,13 @@
           <t>11:37</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Spillkråkehack</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1158,70 +1121,59 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kristina Bäck, Johan Stork, Ronny Fors, Jana Eriksson, Martin Permats</t>
+          <t>Kristina Bäck, Johan Andersson, Ronny Fors, Jana Eriksson, Martin Permats</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>101574328</v>
+        <v>101574878</v>
       </c>
       <c r="B6" t="n">
-        <v>89412</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5442</v>
+        <v>2180</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Nacka, Srm</t>
+          <t>Norr om Sanda, Nacka, Srm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>682650.4870739159</v>
+        <v>682710</v>
       </c>
       <c r="R6" t="n">
-        <v>6575404.927130928</v>
+        <v>6575512</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1250,7 +1202,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1260,7 +1212,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1269,83 +1221,57 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>Hällmarksbarrskog</t>
-        </is>
-      </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Stem on living tree</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Martin Permats</t>
+          <t>Kristina Bäck</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Martin Permats</t>
+          <t>Kristina Bäck, Jana Eriksson, Johan Andersson, Ronny Fors, Martin Permats</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>101574740</v>
+        <v>101575072</v>
       </c>
       <c r="B7" t="n">
-        <v>89412</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5442</v>
+        <v>2180</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1353,10 +1279,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>682681.4215081711</v>
+        <v>682765</v>
       </c>
       <c r="R7" t="n">
-        <v>6575518.507863252</v>
+        <v>6575488</v>
       </c>
       <c r="S7" t="n">
         <v>2</v>
@@ -1419,22 +1345,17 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kristina Bäck, Ronny Fors, Jana Eriksson, Martin Permats, Johan Stork</t>
+          <t>Kristina Bäck, Ronny Fors, Johan Andersson, Martin Permats, Jana Eriksson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>101574543</v>
+        <v>101576764</v>
       </c>
       <c r="B8" t="n">
-        <v>8377</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1442,42 +1363,39 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>106545</v>
+        <v>2180</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Norr om Sanda, Nacka, Srm</t>
+          <t>Sanda, norr om, Srm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>682662.9517774805</v>
+        <v>682893</v>
       </c>
       <c r="R8" t="n">
-        <v>6575476.16044121</v>
+        <v>6575496</v>
       </c>
       <c r="S8" t="n">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1504,55 +1422,39 @@
           <t>2022-06-11</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>11:31</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2022-06-11</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>11:31</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kristina Bäck</t>
+          <t>Johan Andersson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kristina Bäck, Ronny Fors, Johan Stork, Jana Eriksson, Martin Permats</t>
+          <t>Johan Andersson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>112017087</v>
+        <v>101577329</v>
       </c>
       <c r="B9" t="n">
-        <v>8377</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1560,46 +1462,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>106545</v>
+        <v>2180</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>N Mellanberg, Erstavik, Srm</t>
+          <t>Sanda, norr om, Srm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>682658</v>
+        <v>682952</v>
       </c>
       <c r="R9" t="n">
-        <v>6575499</v>
+        <v>6575449</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1623,12 +1518,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2023-09-10</t>
+          <t>2022-06-11</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2023-09-10</t>
+          <t>2022-06-11</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1637,29 +1532,28 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Ronny Fors</t>
+          <t>Johan Andersson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Ronny Fors</t>
+          <t>Johan Andersson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131729213</v>
+        <v>131733784</v>
       </c>
       <c r="B10" t="n">
-        <v>8455</v>
+        <v>92188</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1667,21 +1561,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>106545</v>
+        <v>3008</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Timmerticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Amyloporia sinuosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Rajchenb. &amp; al.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1691,10 +1585,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>682658</v>
+        <v>682892</v>
       </c>
       <c r="R10" t="n">
-        <v>6575490</v>
+        <v>6575499</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1729,11 +1623,6 @@
           <t>2025-10-16</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Äldre gnagspår</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1742,6 +1631,11 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Tall</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1758,15 +1652,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>101576989</v>
+        <v>112017326</v>
       </c>
       <c r="B11" t="n">
-        <v>89412</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1774,44 +1663,40 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5442</v>
+        <v>4362</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>(Hornem.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Norr om Sanda, Nacka, Srm</t>
+          <t>N Mellanberg, Erstavik, Srm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>682931.966279577</v>
+        <v>682714</v>
       </c>
       <c r="R11" t="n">
-        <v>6575458.414300293</v>
+        <v>6575496</v>
       </c>
       <c r="S11" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1835,22 +1720,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2022-06-11</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>12:43</t>
+          <t>2023-09-10</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2022-06-11</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>12:43</t>
+          <t>2023-09-10</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1866,69 +1741,63 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kristina Bäck</t>
+          <t>Ronny Fors</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kristina Bäck, Ronny Fors, Johan Stork, Martin Permats, Jana Eriksson</t>
+          <t>Ronny Fors</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>101575072</v>
+        <v>112017130</v>
       </c>
       <c r="B12" t="n">
-        <v>93375</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2180</v>
+        <v>4364</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Norr om Sanda, Nacka, Srm</t>
+          <t>N Mellanberg, Erstavik, Srm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>682764.9159736893</v>
+        <v>682695</v>
       </c>
       <c r="R12" t="n">
-        <v>6575488.23749305</v>
+        <v>6575453</v>
       </c>
       <c r="S12" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1952,22 +1821,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2022-06-11</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>11:37</t>
+          <t>2023-09-10</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2022-06-11</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>11:37</t>
+          <t>2023-09-10</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1983,80 +1842,63 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kristina Bäck</t>
+          <t>Ronny Fors</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kristina Bäck, Ronny Fors, Johan Stork, Martin Permats, Jana Eriksson</t>
+          <t>Ronny Fors</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>101589135</v>
+        <v>112017252</v>
       </c>
       <c r="B13" t="n">
-        <v>96251</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>219790</v>
+        <v>4364</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Nacka, Srm</t>
+          <t>N Mellanberg, Erstavik, Srm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>683165.6316249722</v>
+        <v>682711</v>
       </c>
       <c r="R13" t="n">
-        <v>6575493.234575982</v>
+        <v>6575494</v>
       </c>
       <c r="S13" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2080,22 +1922,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2022-06-11</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>13:23</t>
+          <t>2023-09-10</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2022-06-11</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>13:23</t>
+          <t>2023-09-10</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2104,80 +1936,70 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
-      </c>
-      <c r="AH13" t="inlineStr">
-        <is>
-          <t>Våtmark</t>
-        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Martin Permats</t>
+          <t>Ronny Fors</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Martin Permats</t>
+          <t>Ronny Fors</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>101574857</v>
+        <v>112017447</v>
       </c>
       <c r="B14" t="n">
-        <v>93375</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2180</v>
+        <v>4364</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Norr om Sanda, Srm</t>
+          <t>N Mellanberg, Erstavik, Srm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>682708.4838155493</v>
+        <v>682844</v>
       </c>
       <c r="R14" t="n">
-        <v>6575520.834938429</v>
+        <v>6575513</v>
       </c>
       <c r="S14" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2201,22 +2023,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2022-06-11</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>11:37</t>
+          <t>2023-09-10</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2022-06-11</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>11:37</t>
+          <t>2023-09-10</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2232,70 +2044,60 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Kristina Bäck</t>
+          <t>Ronny Fors</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Kristina Bäck, Johan Stork, Ronny Fors, Jana Eriksson, Martin Permats</t>
+          <t>Ronny Fors</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>101578301</v>
+        <v>131729209</v>
       </c>
       <c r="B15" t="n">
-        <v>5113</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93271</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100526</v>
+        <v>4364</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Norr om Sanda, Nacka, Srm</t>
+          <t>Erstavik, Srm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>683191.6723238613</v>
+        <v>683048</v>
       </c>
       <c r="R15" t="n">
-        <v>6575410.550240339</v>
+        <v>6575489</v>
       </c>
       <c r="S15" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2319,22 +2121,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2022-06-11</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>14:26</t>
+          <t>2025-10-16</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2022-06-11</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>14:26</t>
+          <t>2025-10-16</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2343,34 +2135,28 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Kristina Bäck</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Kristina Bäck, Ronny Fors, Martin Permats, Jana Eriksson</t>
+          <t>Samuel Persson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>101577019</v>
+        <v>112017224</v>
       </c>
       <c r="B16" t="n">
-        <v>89412</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93209</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2378,48 +2164,40 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5442</v>
+        <v>4366</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Norr om Sanda, Nacka, Srm</t>
+          <t>N Mellanberg, Erstavik, Srm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>682934.5866666588</v>
+        <v>682702</v>
       </c>
       <c r="R16" t="n">
-        <v>6575478.502218832</v>
+        <v>6575491</v>
       </c>
       <c r="S16" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2443,22 +2221,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2022-06-11</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>12:43</t>
+          <t>2023-09-10</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2022-06-11</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>12:43</t>
+          <t>2023-09-10</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2474,67 +2242,63 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Kristina Bäck</t>
+          <t>Ronny Fors</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Kristina Bäck, Ronny Fors, Johan Stork, Jana Eriksson, Martin Permats</t>
+          <t>Ronny Fors</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>101589275</v>
+        <v>112017488</v>
       </c>
       <c r="B17" t="n">
-        <v>95519</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93209</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221945</v>
+        <v>4366</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Nacka, Srm</t>
+          <t>N Mellanberg, Erstavik, Srm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>683165.6316249722</v>
+        <v>682956</v>
       </c>
       <c r="R17" t="n">
-        <v>6575493.234575982</v>
+        <v>6575474</v>
       </c>
       <c r="S17" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2558,22 +2322,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2022-06-11</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>13:23</t>
+          <t>2023-09-10</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2022-06-11</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>13:23</t>
+          <t>2023-09-10</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2582,38 +2336,29 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
-      </c>
-      <c r="AH17" t="inlineStr">
-        <is>
-          <t>Våtmark</t>
-        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Martin Permats</t>
+          <t>Ronny Fors</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Martin Permats</t>
+          <t>Ronny Fors</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>101577442</v>
+        <v>112017566</v>
       </c>
       <c r="B18" t="n">
-        <v>89412</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89138</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2621,48 +2366,40 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5442</v>
+        <v>4404</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Sotvaxskivling</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hygrophorus camarophyllus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) Dumée &amp; al.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Norr om Sanda, Nacka, Srm</t>
+          <t>N Mellanberg, Erstavik, Srm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>683020.7230944174</v>
+        <v>683021</v>
       </c>
       <c r="R18" t="n">
-        <v>6575478.562571427</v>
+        <v>6575443</v>
       </c>
       <c r="S18" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2686,22 +2423,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2022-06-11</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>13:39</t>
+          <t>2023-09-10</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2022-06-11</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>13:39</t>
+          <t>2023-09-10</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2717,27 +2444,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Kristina Bäck</t>
+          <t>Ronny Fors</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Kristina Bäck, Ronny Fors, Johan Stork, Martin Permats, Jana Eriksson</t>
+          <t>Ronny Fors</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>101577625</v>
+        <v>111858253</v>
       </c>
       <c r="B19" t="n">
-        <v>96251</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92348</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2745,43 +2467,48 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>219790</v>
+        <v>5420</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Norr om Sanda, Nacka, Srm</t>
+          <t>NW Erstavik, Srm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>683044.7715829043</v>
+        <v>682892</v>
       </c>
       <c r="R19" t="n">
-        <v>6575468.974419592</v>
+        <v>6575488</v>
       </c>
       <c r="S19" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2805,22 +2532,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2022-06-11</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>13:46</t>
+          <t>2023-09-02</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2022-06-11</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>13:46</t>
+          <t>2023-09-02</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Hällmark, stig; På Tallstubbe, "tung-formad"</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2829,33 +2551,29 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Kristina Bäck</t>
+          <t>Henry Gudmundson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Kristina Bäck</t>
+          <t>Henry Gudmundson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>101575316</v>
+        <v>101574257</v>
       </c>
       <c r="B20" t="n">
-        <v>56411</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2863,38 +2581,45 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Norr om Sanda, Nacka, Srm</t>
+          <t>Norr om Sanda, Srm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>682761.9994682702</v>
+        <v>682663</v>
       </c>
       <c r="R20" t="n">
-        <v>6575474.277554707</v>
+        <v>6575367</v>
       </c>
       <c r="S20" t="n">
         <v>2</v>
@@ -2926,7 +2651,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2936,12 +2661,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>12:09</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Hackspår</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2950,6 +2670,7 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2961,65 +2682,65 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Kristina Bäck, Ronny Fors, Jana Eriksson, Martin Permats, Johan Stork</t>
+          <t>Kristina Bäck, Ronny Fors, Martin Permats, Johan Andersson, Jana Eriksson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>101575253</v>
+        <v>101574327</v>
       </c>
       <c r="B21" t="n">
-        <v>8377</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>106545</v>
+        <v>5442</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Norr om Sanda, Nacka, Srm</t>
+          <t>Nacka, Srm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>682777.8871047667</v>
+        <v>682650</v>
       </c>
       <c r="R21" t="n">
-        <v>6575463.782761714</v>
+        <v>6575405</v>
       </c>
       <c r="S21" t="n">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3048,7 +2769,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3058,7 +2779,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3067,63 +2788,78 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>Hällmarksbarrskog</t>
+        </is>
+      </c>
+      <c r="AM21" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Stem on living tree</t>
+        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Kristina Bäck</t>
+          <t>Martin Permats</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Kristina Bäck, Ronny Fors, Johan Stork, Jana Eriksson, Martin Permats</t>
+          <t>Martin Permats</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>101577080</v>
+        <v>101574354</v>
       </c>
       <c r="B22" t="n">
-        <v>4717</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>102306</v>
+        <v>5442</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -3131,10 +2867,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>682934.5866666588</v>
+        <v>682670</v>
       </c>
       <c r="R22" t="n">
-        <v>6575478.502218832</v>
+        <v>6575428</v>
       </c>
       <c r="S22" t="n">
         <v>2</v>
@@ -3166,7 +2902,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3176,12 +2912,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>12:43</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Hål efter i gran som är döende</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3202,22 +2933,17 @@
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Kristina Bäck, Ronny Fors, Johan Stork, Jana Eriksson, Martin Permats</t>
+          <t>Kristina Bäck, Ronny Fors, Martin Permats, Johan Andersson, Jana Eriksson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>101575295</v>
+        <v>101574465</v>
       </c>
       <c r="B23" t="n">
-        <v>89412</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3244,7 +2970,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -3260,10 +2986,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>682759.775949874</v>
+        <v>682666</v>
       </c>
       <c r="R23" t="n">
-        <v>6575488.501670112</v>
+        <v>6575464</v>
       </c>
       <c r="S23" t="n">
         <v>2</v>
@@ -3295,7 +3021,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3305,7 +3031,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3326,50 +3052,52 @@
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Kristina Bäck, Jana Eriksson, Ronny Fors, Martin Permats, Johan Stork</t>
+          <t>Kristina Bäck, Ronny Fors, Johan Andersson, Martin Permats, Jana Eriksson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>101577753</v>
+        <v>101574740</v>
       </c>
       <c r="B24" t="n">
-        <v>95519</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>221945</v>
+        <v>5442</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3377,10 +3105,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>683078.6567980717</v>
+        <v>682681</v>
       </c>
       <c r="R24" t="n">
-        <v>6575468.050526729</v>
+        <v>6575519</v>
       </c>
       <c r="S24" t="n">
         <v>2</v>
@@ -3412,7 +3140,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3422,7 +3150,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3443,55 +3171,52 @@
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Kristina Bäck, Ronny Fors, Johan Stork, Martin Permats, Jana Eriksson</t>
+          <t>Kristina Bäck, Ronny Fors, Jana Eriksson, Martin Permats, Johan Andersson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>101577998</v>
+        <v>101575295</v>
       </c>
       <c r="B25" t="n">
-        <v>4717</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>102306</v>
+        <v>5442</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3499,10 +3224,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>683132.831303214</v>
+        <v>682760</v>
       </c>
       <c r="R25" t="n">
-        <v>6575471.68927494</v>
+        <v>6575489</v>
       </c>
       <c r="S25" t="n">
         <v>2</v>
@@ -3534,7 +3259,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3544,7 +3269,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3565,67 +3290,55 @@
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Kristina Bäck, Ronny Fors, Johan Stork, Jana Eriksson, Martin Permats</t>
+          <t>Kristina Bäck, Jana Eriksson, Ronny Fors, Martin Permats, Johan Andersson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>101575063</v>
+        <v>131729211</v>
       </c>
       <c r="B26" t="n">
-        <v>8367</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91995</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>106554</v>
+        <v>5442</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Sanda, norr om, Srm</t>
+          <t>Erstavik, Srm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>682734.8529345258</v>
+        <v>682932</v>
       </c>
       <c r="R26" t="n">
-        <v>6575494.97837727</v>
+        <v>6575476</v>
       </c>
       <c r="S26" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3649,22 +3362,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2022-06-11</t>
-        </is>
-      </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-10-16</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2022-06-11</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-10-16</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3679,67 +3382,67 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Johan Stork</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Johan Stork</t>
+          <t>Samuel Persson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>101577329</v>
+        <v>101576989</v>
       </c>
       <c r="B27" t="n">
-        <v>93375</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2180</v>
+        <v>5442</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Sanda, norr om, Srm</t>
+          <t>Norr om Sanda, Nacka, Srm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>682951.9222491342</v>
+        <v>682932</v>
       </c>
       <c r="R27" t="n">
-        <v>6575448.628163522</v>
+        <v>6575458</v>
       </c>
       <c r="S27" t="n">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3768,7 +3471,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3778,7 +3481,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3787,73 +3490,78 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Johan Stork</t>
+          <t>Kristina Bäck</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Johan Stork</t>
+          <t>Kristina Bäck, Ronny Fors, Johan Andersson, Martin Permats, Jana Eriksson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>101576764</v>
+        <v>101577019</v>
       </c>
       <c r="B28" t="n">
-        <v>93375</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2180</v>
+        <v>5442</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Sanda, norr om, Srm</t>
+          <t>Norr om Sanda, Nacka, Srm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>682892.7275595821</v>
+        <v>682935</v>
       </c>
       <c r="R28" t="n">
-        <v>6575495.933338026</v>
+        <v>6575479</v>
       </c>
       <c r="S28" t="n">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3882,7 +3590,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3892,7 +3600,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3901,28 +3609,29 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Johan Stork</t>
+          <t>Kristina Bäck</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Johan Stork</t>
+          <t>Kristina Bäck, Ronny Fors, Johan Andersson, Jana Eriksson, Martin Permats</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131729211</v>
+        <v>101577442</v>
       </c>
       <c r="B29" t="n">
-        <v>91913</v>
+        <v>91930</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3947,20 +3656,31 @@
           <t>(Brot.) Murrill</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr"/>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Erstavik, Srm</t>
+          <t>Norr om Sanda, Nacka, Srm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>682932</v>
+        <v>683021</v>
       </c>
       <c r="R29" t="n">
-        <v>6575476</v>
+        <v>6575479</v>
       </c>
       <c r="S29" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3984,12 +3704,22 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2025-10-16</t>
+          <t>2022-06-11</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2025-10-16</t>
+          <t>2022-06-11</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3998,75 +3728,67 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Kristina Bäck</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Samuel Persson</t>
+          <t>Kristina Bäck, Ronny Fors, Johan Andersson, Martin Permats, Jana Eriksson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>101574878</v>
+        <v>131729207</v>
       </c>
       <c r="B30" t="n">
-        <v>93375</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
-        </is>
+        <v>91995</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>2180</v>
+        <v>5442</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Norr om Sanda, Nacka, Srm</t>
+          <t>Erstavik, Srm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>682710.461164355</v>
+        <v>683082</v>
       </c>
       <c r="R30" t="n">
-        <v>6575511.717336961</v>
+        <v>6575501</v>
       </c>
       <c r="S30" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4090,22 +3812,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2022-06-11</t>
-        </is>
-      </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>11:37</t>
+          <t>2025-10-16</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2022-06-11</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>11:37</t>
+          <t>2025-10-16</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4114,83 +3826,66 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Kristina Bäck</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Kristina Bäck, Jana Eriksson, Johan Stork, Ronny Fors, Martin Permats</t>
+          <t>Samuel Persson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>111858253</v>
+        <v>131729210</v>
       </c>
       <c r="B31" t="n">
-        <v>89936</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91995</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5420</v>
+        <v>5442</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>NW Erstavik, Srm</t>
+          <t>Erstavik, Srm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>682892</v>
+        <v>683025</v>
       </c>
       <c r="R31" t="n">
-        <v>6575488</v>
+        <v>6575474</v>
       </c>
       <c r="S31" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4214,17 +3909,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2023-09-02</t>
+          <t>2025-10-16</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2023-09-02</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Hällmark, stig; På Tallstubbe, "tung-formad"</t>
+          <t>2025-10-16</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4233,56 +3923,50 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Henry Gudmundson</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Henry Gudmundson</t>
+          <t>Samuel Persson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>112017130</v>
+        <v>112017413</v>
       </c>
       <c r="B32" t="n">
-        <v>90815</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93223</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4364</v>
+        <v>5448</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon melaleucus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Sw. ex Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4295,10 +3979,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>682695</v>
+        <v>682734</v>
       </c>
       <c r="R32" t="n">
-        <v>6575454</v>
+        <v>6575482</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4358,49 +4042,36 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>112017512</v>
+        <v>112017430</v>
       </c>
       <c r="B33" t="n">
-        <v>88181</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93223</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6276</v>
+        <v>5448</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Phellodon melaleucus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Sw. ex Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
@@ -4409,10 +4080,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>683037</v>
+        <v>682793</v>
       </c>
       <c r="R33" t="n">
-        <v>6575484</v>
+        <v>6575520</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4472,56 +4143,48 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>112017447</v>
+        <v>128469483</v>
       </c>
       <c r="B34" t="n">
-        <v>90815</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93223</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>4364</v>
+        <v>5448</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon melaleucus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Sw. ex Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>N Mellanberg, Erstavik, Srm</t>
+          <t>Sanda, Sanda, Srm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>682844</v>
+        <v>682802</v>
       </c>
       <c r="R34" t="n">
-        <v>6575514</v>
+        <v>6575540</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4545,48 +4208,52 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2023-09-10</t>
+          <t>2025-09-15</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2023-09-10</t>
+          <t>2025-09-15</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
       <c r="AE34" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF34" t="inlineStr"/>
+        <v>1</v>
+      </c>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Ronny Fors</t>
+          <t>Johan Lilyvalley</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Ronny Fors</t>
+          <t>Johan Lilyvalley</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>112017326</v>
+        <v>131729208</v>
       </c>
       <c r="B35" t="n">
-        <v>90809</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93309</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4594,40 +4261,37 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>4362</v>
+        <v>5966</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>N Mellanberg, Erstavik, Srm</t>
+          <t>Erstavik, Srm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>682714</v>
+        <v>683052</v>
       </c>
       <c r="R35" t="n">
-        <v>6575496</v>
+        <v>6575490</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4651,12 +4315,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2023-09-10</t>
+          <t>2025-10-16</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2023-09-10</t>
+          <t>2025-10-16</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4665,19 +4329,18 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Ronny Fors</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Ronny Fors</t>
+          <t>Samuel Persson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
@@ -4687,12 +4350,7 @@
         <v>112017465</v>
       </c>
       <c r="B36" t="n">
-        <v>88181</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90691</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4798,41 +4456,44 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>112017252</v>
+        <v>112017512</v>
       </c>
       <c r="B37" t="n">
-        <v>90815</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90691</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>4364</v>
+        <v>6276</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K37" t="inlineStr"/>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
@@ -4841,10 +4502,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>682711</v>
+        <v>683037</v>
       </c>
       <c r="R37" t="n">
-        <v>6575494</v>
+        <v>6575485</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4904,15 +4565,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>112017224</v>
+        <v>101574331</v>
       </c>
       <c r="B38" t="n">
-        <v>90827</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4920,40 +4576,41 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>4366</v>
+        <v>100049</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr"/>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>N Mellanberg, Erstavik, Srm</t>
+          <t>Norr om Sanda, Nacka, Srm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>682703</v>
+        <v>682665</v>
       </c>
       <c r="R38" t="n">
-        <v>6575491</v>
+        <v>6575409</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4977,12 +4634,27 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2023-09-10</t>
+          <t>2022-06-11</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2023-09-10</t>
+          <t>2022-06-11</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>11:19</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Spår</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4991,83 +4663,70 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Ronny Fors</t>
+          <t>Kristina Bäck</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Ronny Fors</t>
+          <t>Kristina Bäck, Ronny Fors, Johan Andersson, Martin Permats, Jana Eriksson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>112017534</v>
+        <v>101574766</v>
       </c>
       <c r="B39" t="n">
-        <v>88141</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1593</v>
+        <v>100049</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Lakritsmusseron</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Tricholoma apium</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Jul.Schäff.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr"/>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>N Mellanberg, Erstavik, Srm</t>
+          <t>Norr om Sanda, Nacka, Srm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>683073</v>
+        <v>682681</v>
       </c>
       <c r="R39" t="n">
-        <v>6575478</v>
+        <v>6575519</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5091,12 +4750,27 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2023-09-10</t>
+          <t>2022-06-11</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2023-09-10</t>
+          <t>2022-06-11</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>11:37</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Spillkråkehack</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5105,75 +4779,70 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Ronny Fors</t>
+          <t>Kristina Bäck</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Ronny Fors</t>
+          <t>Kristina Bäck, Johan Andersson, Ronny Fors, Jana Eriksson, Martin Permats</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>112017413</v>
+        <v>101575316</v>
       </c>
       <c r="B40" t="n">
-        <v>90858</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5448</v>
+        <v>100049</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr"/>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>N Mellanberg, Erstavik, Srm</t>
+          <t>Norr om Sanda, Nacka, Srm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>682734</v>
+        <v>682762</v>
       </c>
       <c r="R40" t="n">
-        <v>6575482</v>
+        <v>6575474</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5197,12 +4866,27 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2023-09-10</t>
+          <t>2022-06-11</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2023-09-10</t>
+          <t>2022-06-11</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>12:09</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Hackspår</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5211,34 +4895,28 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Ronny Fors</t>
+          <t>Kristina Bäck</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Ronny Fors</t>
+          <t>Kristina Bäck, Ronny Fors, Jana Eriksson, Martin Permats, Johan Andersson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>112017488</v>
+        <v>101575609</v>
       </c>
       <c r="B41" t="n">
-        <v>90827</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5246,40 +4924,40 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>4366</v>
+        <v>100049</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>N Mellanberg, Erstavik, Srm</t>
+          <t>Nacka, Srm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>682956</v>
+        <v>682800</v>
       </c>
       <c r="R41" t="n">
-        <v>6575474</v>
+        <v>6575446</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5303,12 +4981,22 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2023-09-10</t>
+          <t>2022-06-11</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2023-09-10</t>
+          <t>2022-06-11</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5317,75 +5005,75 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
+      </c>
+      <c r="AH41" t="inlineStr">
+        <is>
+          <t>Hällmarksbarrskog</t>
+        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Ronny Fors</t>
+          <t>Martin Permats</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Ronny Fors</t>
+          <t>Martin Permats</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>112017159</v>
+        <v>101575751</v>
       </c>
       <c r="B42" t="n">
-        <v>90859</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57258</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>5449</v>
+        <v>100065</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Trana</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Grus grus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr"/>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>N Mellanberg, Erstavik, Srm</t>
+          <t>Norr om Sanda, Nacka, Srm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>682699</v>
+        <v>682769</v>
       </c>
       <c r="R42" t="n">
-        <v>6575482</v>
+        <v>6575432</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5409,12 +5097,22 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2023-09-10</t>
+          <t>2022-06-11</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2023-09-10</t>
+          <t>2022-06-11</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5423,75 +5121,71 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Ronny Fors</t>
+          <t>Kristina Bäck</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Ronny Fors</t>
+          <t>Kristina Bäck, Ronny Fors, Johan Andersson, Jana Eriksson, Martin Permats</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>112017392</v>
+        <v>101578301</v>
       </c>
       <c r="B43" t="n">
-        <v>90859</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5179</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>5449</v>
+        <v>100526</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr"/>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>N Mellanberg, Erstavik, Srm</t>
+          <t>Norr om Sanda, Nacka, Srm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>682712</v>
+        <v>683192</v>
       </c>
       <c r="R43" t="n">
-        <v>6575458</v>
+        <v>6575411</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5515,12 +5209,22 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2023-09-10</t>
+          <t>2022-06-11</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2023-09-10</t>
+          <t>2022-06-11</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5536,68 +5240,65 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Ronny Fors</t>
+          <t>Kristina Bäck</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Ronny Fors</t>
+          <t>Kristina Bäck, Ronny Fors, Martin Permats, Jana Eriksson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>112017430</v>
+        <v>101577080</v>
       </c>
       <c r="B44" t="n">
-        <v>90858</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>4781</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>5448</v>
+        <v>102306</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr"/>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>N Mellanberg, Erstavik, Srm</t>
+          <t>Norr om Sanda, Nacka, Srm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>682793</v>
+        <v>682935</v>
       </c>
       <c r="R44" t="n">
-        <v>6575520</v>
+        <v>6575479</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5621,12 +5322,27 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2023-09-10</t>
+          <t>2022-06-11</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2023-09-10</t>
+          <t>2022-06-11</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>12:43</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Hål efter i gran som är döende</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5642,60 +5358,69 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Ronny Fors</t>
+          <t>Kristina Bäck</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Ronny Fors</t>
+          <t>Kristina Bäck, Ronny Fors, Johan Andersson, Jana Eriksson, Martin Permats</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>131729207</v>
+        <v>101577998</v>
       </c>
       <c r="B45" t="n">
-        <v>91913</v>
+        <v>4781</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>5442</v>
+        <v>102306</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Erstavik, Srm</t>
+          <t>Norr om Sanda, Nacka, Srm</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>683082</v>
+        <v>683133</v>
       </c>
       <c r="R45" t="n">
-        <v>6575501</v>
+        <v>6575472</v>
       </c>
       <c r="S45" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5719,12 +5444,22 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2025-10-16</t>
+          <t>2022-06-11</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2025-10-16</t>
+          <t>2022-06-11</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5733,50 +5468,51 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Kristina Bäck</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Samuel Persson</t>
+          <t>Kristina Bäck, Ronny Fors, Johan Andersson, Jana Eriksson, Martin Permats</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>131729210</v>
+        <v>131729215</v>
       </c>
       <c r="B46" t="n">
-        <v>91913</v>
+        <v>58250</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>5442</v>
+        <v>103019</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Stjärtmes</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Aegithalos caudatus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5786,10 +5522,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>683025</v>
+        <v>682638</v>
       </c>
       <c r="R46" t="n">
-        <v>6575474</v>
+        <v>6575543</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5832,6 +5568,14 @@
       </c>
       <c r="AG46" t="b">
         <v>0</v>
+      </c>
+      <c r="AN46" t="n">
+        <v>8</v>
+      </c>
+      <c r="AO46" t="inlineStr">
+        <is>
+          <t>8 substratenheter</t>
+        </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
@@ -5848,48 +5592,52 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>131729208</v>
+        <v>101575743</v>
       </c>
       <c r="B47" t="n">
-        <v>93218</v>
+        <v>58636</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>5966</v>
+        <v>103044</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Erstavik, Srm</t>
+          <t>Norr om Sanda, Nacka, Srm</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>683052</v>
+        <v>682769</v>
       </c>
       <c r="R47" t="n">
-        <v>6575490</v>
+        <v>6575432</v>
       </c>
       <c r="S47" t="n">
-        <v>5</v>
+        <v>40</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5913,12 +5661,22 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2025-10-16</t>
+          <t>2022-06-11</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2025-10-16</t>
+          <t>2022-06-11</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5933,22 +5691,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Kristina Bäck</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Samuel Persson</t>
+          <t>Kristina Bäck, Ronny Fors, Johan Andersson, Jana Eriksson, Martin Permats</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>131729209</v>
+        <v>101574543</v>
       </c>
       <c r="B48" t="n">
-        <v>93180</v>
+        <v>8455</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5956,37 +5714,42 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>4364</v>
+        <v>106545</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Erstavik, Srm</t>
+          <t>Norr om Sanda, Nacka, Srm</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>683048</v>
+        <v>682663</v>
       </c>
       <c r="R48" t="n">
-        <v>6575489</v>
+        <v>6575476</v>
       </c>
       <c r="S48" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6010,12 +5773,22 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2025-10-16</t>
+          <t>2022-06-11</t>
+        </is>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2025-10-16</t>
+          <t>2022-06-11</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6024,21 +5797,914 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
+      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
+          <t>Kristina Bäck</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Kristina Bäck, Ronny Fors, Johan Andersson, Jana Eriksson, Martin Permats</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>101575253</v>
+      </c>
+      <c r="B49" t="n">
+        <v>8455</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr"/>
+      <c r="N49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Norr om Sanda, Nacka, Srm</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>682778</v>
+      </c>
+      <c r="R49" t="n">
+        <v>6575464</v>
+      </c>
+      <c r="S49" t="n">
+        <v>2</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Nacka</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Nacka</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2022-06-11</t>
+        </is>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>12:07</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2022-06-11</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>12:07</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF49" t="inlineStr"/>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Kristina Bäck</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Kristina Bäck, Ronny Fors, Johan Andersson, Jana Eriksson, Martin Permats</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>112017087</v>
+      </c>
+      <c r="B50" t="n">
+        <v>8455</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>N Mellanberg, Erstavik, Srm</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>682658</v>
+      </c>
+      <c r="R50" t="n">
+        <v>6575499</v>
+      </c>
+      <c r="S50" t="n">
+        <v>10</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Nacka</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Nacka</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2023-09-10</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2023-09-10</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF50" t="inlineStr"/>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Ronny Fors</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Ronny Fors</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>131729213</v>
+      </c>
+      <c r="B51" t="n">
+        <v>8460</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Erstavik, Srm</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>682658</v>
+      </c>
+      <c r="R51" t="n">
+        <v>6575490</v>
+      </c>
+      <c r="S51" t="n">
+        <v>5</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Nacka</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Nacka</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
           <t>Johan Kjetselberg</t>
         </is>
       </c>
-      <c r="AX48" t="inlineStr">
+      <c r="AX51" t="inlineStr">
         <is>
           <t>Samuel Persson</t>
         </is>
       </c>
-      <c r="AY48" t="inlineStr"/>
+      <c r="AY51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>101575063</v>
+      </c>
+      <c r="B52" t="n">
+        <v>8444</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Sanda, norr om, Srm</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>682735</v>
+      </c>
+      <c r="R52" t="n">
+        <v>6575495</v>
+      </c>
+      <c r="S52" t="n">
+        <v>25</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Nacka</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Nacka</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2022-06-11</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2022-06-11</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Johan Andersson</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Johan Andersson</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>101577625</v>
+      </c>
+      <c r="B53" t="n">
+        <v>99035</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Norr om Sanda, Nacka, Srm</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>683045</v>
+      </c>
+      <c r="R53" t="n">
+        <v>6575469</v>
+      </c>
+      <c r="S53" t="n">
+        <v>25</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Nacka</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Nacka</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2022-06-11</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>13:46</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2022-06-11</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>13:46</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Kristina Bäck</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Kristina Bäck</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>101589135</v>
+      </c>
+      <c r="B54" t="n">
+        <v>99035</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Nacka, Srm</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>683166</v>
+      </c>
+      <c r="R54" t="n">
+        <v>6575493</v>
+      </c>
+      <c r="S54" t="n">
+        <v>25</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Nacka</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Nacka</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2022-06-11</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>13:23</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2022-06-11</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>13:23</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH54" t="inlineStr">
+        <is>
+          <t>Våtmark</t>
+        </is>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Martin Permats</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Martin Permats</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>101577753</v>
+      </c>
+      <c r="B55" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Norr om Sanda, Nacka, Srm</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>683079</v>
+      </c>
+      <c r="R55" t="n">
+        <v>6575468</v>
+      </c>
+      <c r="S55" t="n">
+        <v>2</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Nacka</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Nacka</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2022-06-11</t>
+        </is>
+      </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>13:46</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2022-06-11</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>13:46</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF55" t="inlineStr"/>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Kristina Bäck</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Kristina Bäck, Ronny Fors, Johan Andersson, Martin Permats, Jana Eriksson</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>101589275</v>
+      </c>
+      <c r="B56" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Nacka, Srm</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>683166</v>
+      </c>
+      <c r="R56" t="n">
+        <v>6575493</v>
+      </c>
+      <c r="S56" t="n">
+        <v>25</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Nacka</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Nacka</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2022-06-11</t>
+        </is>
+      </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>13:23</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2022-06-11</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>13:23</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH56" t="inlineStr">
+        <is>
+          <t>Våtmark</t>
+        </is>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Martin Permats</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Martin Permats</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
